--- a/Team-Data/2012-13/1-30-2012-13.xlsx
+++ b/Team-Data/2012-13/1-30-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,58 +728,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.578</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>48.7</v>
       </c>
       <c r="I2" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L2" t="n">
         <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="N2" t="n">
         <v>0.382</v>
       </c>
       <c r="O2" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="P2" t="n">
         <v>19.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="R2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>30.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U2" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V2" t="n">
         <v>15.1</v>
@@ -721,7 +788,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
         <v>4.7</v>
@@ -733,19 +800,19 @@
         <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AC2" t="n">
         <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -757,7 +824,7 @@
         <v>13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>6</v>
@@ -769,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
@@ -784,25 +851,25 @@
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
         <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV2" t="n">
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -811,7 +878,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
         <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.489</v>
+        <v>0.477</v>
       </c>
       <c r="H3" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="I3" t="n">
         <v>36.7</v>
       </c>
       <c r="J3" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L3" t="n">
         <v>5.4</v>
@@ -873,19 +940,19 @@
         <v>16.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="O3" t="n">
         <v>16.4</v>
       </c>
       <c r="P3" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
         <v>0.782</v>
       </c>
       <c r="R3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>31</v>
@@ -894,10 +961,10 @@
         <v>39.6</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V3" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W3" t="n">
         <v>8.699999999999999</v>
@@ -906,7 +973,7 @@
         <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z3" t="n">
         <v>21.6</v>
@@ -915,19 +982,19 @@
         <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
         <v>17</v>
@@ -936,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL3" t="n">
         <v>28</v>
@@ -957,7 +1024,7 @@
         <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ3" t="n">
         <v>7</v>
@@ -966,7 +1033,7 @@
         <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -975,7 +1042,7 @@
         <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
@@ -996,7 +1063,7 @@
         <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
         <v>27</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>0.587</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J4" t="n">
-        <v>79.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K4" t="n">
         <v>0.443</v>
@@ -1052,10 +1119,10 @@
         <v>7.7</v>
       </c>
       <c r="M4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O4" t="n">
         <v>18.1</v>
@@ -1070,16 +1137,16 @@
         <v>12.4</v>
       </c>
       <c r="S4" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="T4" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="U4" t="n">
         <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
         <v>7.2</v>
@@ -1091,31 +1158,31 @@
         <v>4.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA4" t="n">
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,16 +1200,16 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>9</v>
@@ -1151,13 +1218,13 @@
         <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1166,7 +1233,7 @@
         <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ4" t="n">
         <v>4</v>
@@ -1178,7 +1245,7 @@
         <v>17</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -1207,91 +1274,91 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.244</v>
+        <v>0.25</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.424</v>
+        <v>0.425</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.35</v>
+        <v>0.354</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P5" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S5" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="T5" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U5" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="V5" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X5" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA5" t="n">
         <v>21.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.4</v>
+        <v>-8</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
         <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
         <v>30</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1330,7 +1397,7 @@
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
         <v>22</v>
@@ -1339,25 +1406,25 @@
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.622</v>
+        <v>0.614</v>
       </c>
       <c r="H6" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="J6" t="n">
-        <v>80.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L6" t="n">
         <v>4.8</v>
@@ -1419,34 +1486,34 @@
         <v>13.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O6" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="P6" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R6" t="n">
         <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T6" t="n">
         <v>44</v>
       </c>
       <c r="U6" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V6" t="n">
         <v>14.8</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X6" t="n">
         <v>5.5</v>
@@ -1455,31 +1522,31 @@
         <v>5.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" t="n">
         <v>20.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.59999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
         <v>7</v>
       </c>
       <c r="AG6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
@@ -1488,7 +1555,7 @@
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1497,10 +1564,10 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP6" t="n">
         <v>11</v>
@@ -1515,34 +1582,34 @@
         <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
         <v>25</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG7" t="n">
         <v>28</v>
@@ -1679,7 +1746,7 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1688,7 +1755,7 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
         <v>6</v>
@@ -1700,10 +1767,10 @@
         <v>21</v>
       </c>
       <c r="AU7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -1831,13 +1898,13 @@
         <v>-2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
       </c>
       <c r="AF8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
         <v>19</v>
@@ -1858,16 +1925,16 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN8" t="n">
         <v>10</v>
       </c>
       <c r="AO8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1876,7 +1943,7 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
@@ -1888,7 +1955,7 @@
         <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX8" t="n">
         <v>17</v>
@@ -1897,13 +1964,13 @@
         <v>8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
         <v>22</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
         <v>22</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -1935,61 +2002,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.617</v>
+        <v>0.609</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="J9" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L9" t="n">
         <v>6.4</v>
       </c>
       <c r="M9" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.336</v>
+        <v>0.338</v>
       </c>
       <c r="O9" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="S9" t="n">
         <v>31.9</v>
       </c>
       <c r="T9" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="U9" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V9" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W9" t="n">
         <v>8.5</v>
@@ -1998,25 +2065,25 @@
         <v>6.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.8</v>
+        <v>103.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
         <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
         <v>9</v>
@@ -2028,7 +2095,7 @@
         <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -2037,16 +2104,16 @@
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM9" t="n">
         <v>18</v>
       </c>
       <c r="AN9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
         <v>4</v>
@@ -2061,10 +2128,10 @@
         <v>10</v>
       </c>
       <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
         <v>2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3</v>
       </c>
       <c r="AV9" t="n">
         <v>28</v>
@@ -2073,7 +2140,7 @@
         <v>7</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -2117,58 +2184,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="n">
         <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>0.37</v>
+        <v>0.378</v>
       </c>
       <c r="H10" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J10" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M10" t="n">
         <v>16.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.368</v>
+        <v>0.372</v>
       </c>
       <c r="O10" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P10" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.702</v>
+        <v>0.708</v>
       </c>
       <c r="R10" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="n">
         <v>43.5</v>
       </c>
       <c r="U10" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V10" t="n">
         <v>15.2</v>
@@ -2177,25 +2244,25 @@
         <v>6.4</v>
       </c>
       <c r="X10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z10" t="n">
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,16 +2274,16 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
@@ -2246,31 +2313,31 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB10" t="n">
         <v>22</v>
       </c>
-      <c r="AW10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>23</v>
-      </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
@@ -2389,7 +2456,7 @@
         <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2404,16 +2471,16 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2428,7 +2495,7 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
         <v>24</v>
@@ -2437,7 +2504,7 @@
         <v>26</v>
       </c>
       <c r="AX11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY11" t="n">
         <v>18</v>
@@ -2446,13 +2513,13 @@
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB11" t="n">
         <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.521</v>
+        <v>0.532</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,28 +2566,28 @@
         <v>37.8</v>
       </c>
       <c r="J12" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.456</v>
       </c>
       <c r="L12" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="M12" t="n">
         <v>28.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O12" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P12" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R12" t="n">
         <v>10.8</v>
@@ -2535,10 +2602,10 @@
         <v>22.7</v>
       </c>
       <c r="V12" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="W12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X12" t="n">
         <v>4.1</v>
@@ -2547,25 +2614,25 @@
         <v>6.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>105</v>
+        <v>104.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
         <v>15</v>
@@ -2589,13 +2656,13 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>14</v>
@@ -2604,7 +2671,7 @@
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -2616,25 +2683,25 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA12" t="n">
         <v>17</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>16</v>
       </c>
       <c r="BB12" t="n">
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -2663,58 +2730,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
         <v>19</v>
       </c>
       <c r="G13" t="n">
-        <v>0.587</v>
+        <v>0.578</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J13" t="n">
         <v>81.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L13" t="n">
         <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O13" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P13" t="n">
         <v>21.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.743</v>
+        <v>0.739</v>
       </c>
       <c r="R13" t="n">
         <v>13.1</v>
       </c>
       <c r="S13" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T13" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
       <c r="U13" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V13" t="n">
         <v>15.2</v>
@@ -2723,43 +2790,43 @@
         <v>6.8</v>
       </c>
       <c r="X13" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>91.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2768,13 +2835,13 @@
         <v>17</v>
       </c>
       <c r="AM13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP13" t="n">
         <v>18</v>
@@ -2786,16 +2853,16 @@
         <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="n">
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2804,19 +2871,19 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -2845,58 +2912,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.723</v>
+        <v>0.717</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J14" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
       </c>
       <c r="L14" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O14" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="R14" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S14" t="n">
         <v>30.3</v>
       </c>
       <c r="T14" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
         <v>14.3</v>
@@ -2905,19 +2972,19 @@
         <v>10.1</v>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y14" t="n">
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="AC14" t="n">
         <v>7.7</v>
@@ -2926,7 +2993,7 @@
         <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
@@ -2941,25 +3008,25 @@
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN14" t="n">
         <v>18</v>
       </c>
       <c r="AO14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
         <v>26</v>
@@ -2971,13 +3038,13 @@
         <v>18</v>
       </c>
       <c r="AT14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" t="n">
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>0.435</v>
+        <v>0.444</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3048,7 +3115,7 @@
         <v>81.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L15" t="n">
         <v>8.800000000000001</v>
@@ -3057,16 +3124,16 @@
         <v>24.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="P15" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>12.1</v>
@@ -3081,7 +3148,7 @@
         <v>22.2</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
         <v>7.3</v>
@@ -3090,22 +3157,22 @@
         <v>5.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.2</v>
+        <v>102.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
@@ -3126,7 +3193,7 @@
         <v>20</v>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
@@ -3138,7 +3205,7 @@
         <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -3156,19 +3223,19 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>5</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3305,7 +3372,7 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AK16" t="n">
         <v>24</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>21</v>
@@ -3341,7 +3408,7 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3353,13 +3420,13 @@
         <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
         <v>20</v>
       </c>
       <c r="BB16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -3391,61 +3458,61 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="n">
         <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>48.7</v>
       </c>
       <c r="I17" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J17" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="K17" t="n">
         <v>0.489</v>
       </c>
       <c r="L17" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>21.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.386</v>
+        <v>0.382</v>
       </c>
       <c r="O17" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.756</v>
+        <v>0.759</v>
       </c>
       <c r="R17" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T17" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="U17" t="n">
         <v>22.4</v>
       </c>
       <c r="V17" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W17" t="n">
         <v>8.300000000000001</v>
@@ -3454,25 +3521,25 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Z17" t="n">
         <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB17" t="n">
         <v>102.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AD17" t="n">
         <v>29</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
@@ -3487,7 +3554,7 @@
         <v>3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
         <v>1</v>
@@ -3499,10 +3566,10 @@
         <v>9</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3514,7 +3581,7 @@
         <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3526,7 +3593,7 @@
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" t="n">
         <v>24</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.545</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
@@ -3591,25 +3658,25 @@
         <v>37.7</v>
       </c>
       <c r="J18" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.435</v>
       </c>
       <c r="L18" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M18" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O18" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q18" t="n">
         <v>0.738</v>
@@ -3618,19 +3685,19 @@
         <v>13.1</v>
       </c>
       <c r="S18" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T18" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U18" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W18" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X18" t="n">
         <v>7.5</v>
@@ -3642,22 +3709,22 @@
         <v>19.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.8</v>
+        <v>98</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
@@ -3666,7 +3733,7 @@
         <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3681,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
         <v>22</v>
@@ -3696,7 +3763,7 @@
         <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
@@ -3705,16 +3772,16 @@
         <v>14</v>
       </c>
       <c r="AV18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
         <v>1</v>
       </c>
       <c r="AY18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ18" t="n">
         <v>8</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" t="n">
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>0.405</v>
+        <v>0.415</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J19" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K19" t="n">
         <v>0.431</v>
@@ -3782,10 +3849,10 @@
         <v>5.5</v>
       </c>
       <c r="M19" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.295</v>
+        <v>0.296</v>
       </c>
       <c r="O19" t="n">
         <v>18.7</v>
@@ -3794,43 +3861,43 @@
         <v>25.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R19" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="S19" t="n">
         <v>30.7</v>
       </c>
       <c r="T19" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U19" t="n">
         <v>21.8</v>
       </c>
       <c r="V19" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W19" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X19" t="n">
         <v>5.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD19" t="n">
         <v>29</v>
@@ -3842,7 +3909,7 @@
         <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
         <v>27</v>
@@ -3851,7 +3918,7 @@
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3866,10 +3933,10 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
         <v>24</v>
@@ -3878,10 +3945,10 @@
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
         <v>18</v>
@@ -3893,7 +3960,7 @@
         <v>17</v>
       </c>
       <c r="AX19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
         <v>24</v>
@@ -3905,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -3937,34 +4004,34 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
-        <v>0.326</v>
+        <v>0.333</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J20" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L20" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N20" t="n">
         <v>0.374</v>
@@ -3973,16 +4040,16 @@
         <v>14.6</v>
       </c>
       <c r="P20" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.767</v>
+        <v>0.773</v>
       </c>
       <c r="R20" t="n">
         <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T20" t="n">
         <v>41.6</v>
@@ -3991,46 +4058,46 @@
         <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W20" t="n">
         <v>6.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y20" t="n">
         <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AC20" t="n">
         <v>-3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
@@ -4039,7 +4106,7 @@
         <v>14</v>
       </c>
       <c r="AL20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM20" t="n">
         <v>19</v>
@@ -4069,19 +4136,19 @@
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
         <v>26</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -4119,88 +4186,88 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F21" t="n">
         <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>0.651</v>
+        <v>0.643</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>37</v>
+        <v>36.7</v>
       </c>
       <c r="J21" t="n">
         <v>83</v>
       </c>
       <c r="K21" t="n">
-        <v>0.445</v>
+        <v>0.442</v>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="M21" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="O21" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="P21" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R21" t="n">
         <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="V21" t="n">
         <v>11.3</v>
       </c>
       <c r="W21" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X21" t="n">
         <v>3.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z21" t="n">
         <v>19.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>100.7</v>
+        <v>100.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD21" t="n">
         <v>28</v>
       </c>
       <c r="AE21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF21" t="n">
         <v>5</v>
@@ -4218,7 +4285,7 @@
         <v>8</v>
       </c>
       <c r="AK21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,16 +4294,16 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
         <v>21</v>
@@ -4248,13 +4315,13 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
         <v>29</v>
@@ -4269,7 +4336,7 @@
         <v>18</v>
       </c>
       <c r="BB21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC21" t="n">
         <v>5</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>8.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,25 +4458,25 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI22" t="n">
         <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM22" t="n">
         <v>13</v>
       </c>
       <c r="AN22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4427,7 +4494,7 @@
         <v>7</v>
       </c>
       <c r="AT22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
         <v>19</v>
@@ -4454,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="BC22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0.311</v>
+        <v>0.318</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
@@ -4501,19 +4568,19 @@
         <v>37.7</v>
       </c>
       <c r="J23" t="n">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.353</v>
+        <v>0.356</v>
       </c>
       <c r="O23" t="n">
         <v>12.6</v>
@@ -4522,34 +4589,34 @@
         <v>16</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.787</v>
+        <v>0.785</v>
       </c>
       <c r="R23" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S23" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T23" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
       <c r="U23" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
         <v>4.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA23" t="n">
         <v>16.6</v>
@@ -4558,16 +4625,16 @@
         <v>95</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4.2</v>
+        <v>-4</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
         <v>27</v>
       </c>
       <c r="AF23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
         <v>27</v>
@@ -4576,10 +4643,10 @@
         <v>20</v>
       </c>
       <c r="AI23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK23" t="n">
         <v>11</v>
@@ -4588,10 +4655,10 @@
         <v>16</v>
       </c>
       <c r="AM23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4600,13 +4667,13 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR23" t="n">
         <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
         <v>13</v>
@@ -4615,7 +4682,7 @@
         <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4636,7 +4703,7 @@
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
         <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>0.422</v>
+        <v>0.409</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,46 +4750,46 @@
         <v>37.4</v>
       </c>
       <c r="J24" t="n">
-        <v>84.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L24" t="n">
         <v>6.4</v>
       </c>
       <c r="M24" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O24" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="P24" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.718</v>
+        <v>0.72</v>
       </c>
       <c r="R24" t="n">
         <v>10.6</v>
       </c>
       <c r="S24" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T24" t="n">
         <v>40.8</v>
       </c>
       <c r="U24" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V24" t="n">
         <v>12.8</v>
       </c>
       <c r="W24" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X24" t="n">
         <v>5.1</v>
@@ -4731,7 +4798,7 @@
         <v>4.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA24" t="n">
         <v>16.8</v>
@@ -4740,40 +4807,40 @@
         <v>93.40000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
         <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="n">
         <v>24</v>
       </c>
       <c r="AN24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4794,13 +4861,13 @@
         <v>23</v>
       </c>
       <c r="AU24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
         <v>16</v>
@@ -4815,7 +4882,7 @@
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>0.348</v>
+        <v>0.333</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4871,43 +4938,43 @@
         <v>0.445</v>
       </c>
       <c r="L25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="N25" t="n">
-        <v>0.33</v>
+        <v>0.332</v>
       </c>
       <c r="O25" t="n">
         <v>14.9</v>
       </c>
       <c r="P25" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.751</v>
+        <v>0.749</v>
       </c>
       <c r="R25" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S25" t="n">
         <v>29.3</v>
       </c>
       <c r="T25" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U25" t="n">
         <v>22.1</v>
       </c>
       <c r="V25" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W25" t="n">
         <v>7.8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y25" t="n">
         <v>5.1</v>
@@ -4919,34 +4986,34 @@
         <v>18.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4</v>
+        <v>-4.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
@@ -4958,13 +5025,13 @@
         <v>29</v>
       </c>
       <c r="AO25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP25" t="n">
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
         <v>17</v>
@@ -4979,19 +5046,19 @@
         <v>17</v>
       </c>
       <c r="AV25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY25" t="n">
         <v>16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
@@ -5000,7 +5067,7 @@
         <v>18</v>
       </c>
       <c r="BC25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO26" t="n">
         <v>17</v>
@@ -5161,7 +5228,7 @@
         <v>22</v>
       </c>
       <c r="AV26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW26" t="n">
         <v>18</v>
@@ -5182,7 +5249,7 @@
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -5211,31 +5278,31 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" t="n">
         <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G27" t="n">
-        <v>0.362</v>
+        <v>0.37</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="J27" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L27" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M27" t="n">
         <v>18.6</v>
@@ -5247,28 +5314,28 @@
         <v>17</v>
       </c>
       <c r="P27" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="R27" t="n">
         <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="T27" t="n">
         <v>40.5</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V27" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X27" t="n">
         <v>4.6</v>
@@ -5277,16 +5344,16 @@
         <v>6.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.5</v>
+        <v>-6.3</v>
       </c>
       <c r="AD27" t="n">
         <v>3</v>
@@ -5310,7 +5377,7 @@
         <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="n">
         <v>18</v>
@@ -5319,10 +5386,10 @@
         <v>20</v>
       </c>
       <c r="AN27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
@@ -5340,10 +5407,10 @@
         <v>24</v>
       </c>
       <c r="AU27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
@@ -5355,13 +5422,13 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E28" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.771</v>
+        <v>0.766</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="J28" t="n">
-        <v>81.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L28" t="n">
         <v>8.6</v>
       </c>
       <c r="M28" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.382</v>
+        <v>0.379</v>
       </c>
       <c r="O28" t="n">
         <v>16.3</v>
@@ -5432,7 +5499,7 @@
         <v>20.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R28" t="n">
         <v>8.1</v>
@@ -5441,16 +5508,16 @@
         <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U28" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X28" t="n">
         <v>5.1</v>
@@ -5462,13 +5529,13 @@
         <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.3</v>
+        <v>104.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -5486,10 +5553,10 @@
         <v>12</v>
       </c>
       <c r="AI28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5510,7 +5577,7 @@
         <v>23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5525,16 +5592,16 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX28" t="n">
         <v>15</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5546,7 +5613,7 @@
         <v>3</v>
       </c>
       <c r="BC28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G29" t="n">
-        <v>0.348</v>
+        <v>0.356</v>
       </c>
       <c r="H29" t="n">
         <v>49</v>
       </c>
       <c r="I29" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J29" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L29" t="n">
         <v>7.6</v>
@@ -5605,7 +5672,7 @@
         <v>21.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O29" t="n">
         <v>17</v>
@@ -5614,46 +5681,46 @@
         <v>22</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.772</v>
+        <v>0.773</v>
       </c>
       <c r="R29" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S29" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="T29" t="n">
-        <v>40</v>
+        <v>39.7</v>
       </c>
       <c r="U29" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V29" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X29" t="n">
         <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA29" t="n">
         <v>19.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC29" t="n">
         <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>24</v>
@@ -5668,13 +5735,13 @@
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
         <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL29" t="n">
         <v>10</v>
@@ -5683,10 +5750,10 @@
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5704,13 +5771,13 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
         <v>24</v>
@@ -5728,7 +5795,7 @@
         <v>13</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
         <v>21</v>
       </c>
       <c r="G30" t="n">
-        <v>0.543</v>
+        <v>0.533</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
@@ -5775,37 +5842,37 @@
         <v>36.7</v>
       </c>
       <c r="J30" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="K30" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L30" t="n">
         <v>6.2</v>
       </c>
       <c r="M30" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O30" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="P30" t="n">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.764</v>
+        <v>0.767</v>
       </c>
       <c r="R30" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S30" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T30" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U30" t="n">
         <v>22.9</v>
@@ -5826,19 +5893,19 @@
         <v>21.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF30" t="n">
         <v>14</v>
@@ -5847,10 +5914,10 @@
         <v>14</v>
       </c>
       <c r="AH30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI30" t="n">
         <v>16</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>17</v>
       </c>
       <c r="AJ30" t="n">
         <v>16</v>
@@ -5868,7 +5935,7 @@
         <v>9</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
         <v>7</v>
@@ -5877,10 +5944,10 @@
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT30" t="n">
         <v>17</v>
@@ -5889,7 +5956,7 @@
         <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>8</v>
@@ -5898,19 +5965,19 @@
         <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ30" t="n">
         <v>26</v>
       </c>
       <c r="BA30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
       </c>
       <c r="BC30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" t="n">
         <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G31" t="n">
-        <v>0.25</v>
+        <v>0.256</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J31" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0.422</v>
@@ -5966,37 +6033,37 @@
         <v>6.5</v>
       </c>
       <c r="M31" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O31" t="n">
         <v>14.9</v>
       </c>
       <c r="P31" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="R31" t="n">
         <v>11.1</v>
       </c>
       <c r="S31" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T31" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U31" t="n">
         <v>21.5</v>
       </c>
       <c r="V31" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.8</v>
@@ -6005,19 +6072,19 @@
         <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>91.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-4.9</v>
+        <v>-4.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6035,7 +6102,7 @@
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6050,7 +6117,7 @@
         <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
         <v>25</v>
@@ -6062,7 +6129,7 @@
         <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT31" t="n">
         <v>8</v>
@@ -6074,19 +6141,19 @@
         <v>26</v>
       </c>
       <c r="AW31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX31" t="n">
         <v>21</v>
       </c>
       <c r="AY31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-30-2012-13</t>
+          <t>2013-01-30</t>
         </is>
       </c>
     </row>
